--- a/Files/DOC_REQ_NORMA_IEEE_830_ACT_IEEE_29148_RUTAS_MTC.xlsx
+++ b/Files/DOC_REQ_NORMA_IEEE_830_ACT_IEEE_29148_RUTAS_MTC.xlsx
@@ -23905,7 +23905,7 @@
     <t>Linea de Mando</t>
   </si>
   <si>
-    <t>Reporta a: Jefe del Proyecto – Fabián Guerra</t>
+    <t>Reporta a: Jefe del Proyecto – Marcelo Tapia</t>
   </si>
   <si>
     <t>Nivel estratégico-funcional; canaliza al MTC la validación de los requerimientos levantados.</t>
@@ -24011,7 +24011,7 @@
     <t>Designación del especialista: jefe del proyecto.</t>
   </si>
   <si>
-    <t>Nombre: Fabián Guerra</t>
+    <t>Nombre: Marcelo Tapia</t>
   </si>
   <si>
     <t>Responsable máximo de la planificación, ejecución y cierre del proyecto e interlocutor ante el MTC.</t>
@@ -24494,7 +24494,7 @@
     <t>Creado por:</t>
   </si>
   <si>
-    <t>Fabián Guerra (Jefe de Proyecto) · Marcelo Tapia (Analista de Negocios)</t>
+    <t>Marcelo Tapia (Jefe de Proyecto · Analista de Negocios)</t>
   </si>
   <si>
     <t>Ricardo Yanapa (Desarrollador)</t>
